--- a/Employee_Reports_wi48/Gabuin James Buintim Q0396.xlsx
+++ b/Employee_Reports_wi48/Gabuin James Buintim Q0396.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -606,11 +606,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-354</v>
+        <v>-357</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
